--- a/reports/pdf_rolling5_20260727.xlsx
+++ b/reports/pdf_rolling5_20260727.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-20 ~ 2026-07-27  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-20 ~ 2026-07-27  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,394억   ·   현금 59억(1.5%)      오늘 2026-07-27  vs  5일전 2026-07-20      매수 16종목  /  매도 20종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,032억   ·   현금 59억(1.5%)      오늘 2026-07-27  vs  5일전 2026-07-20      매수 16종목  /  매도 20종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>344</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1438102320</v>
+        <v>1439550560</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-50</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-590835000</v>
+        <v>-591430000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1090512600</v>
+        <v>1091610800</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-39</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1248945750</v>
+        <v>-1250203500</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1335982200</v>
+        <v>1337327600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-35</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1522269000</v>
+        <v>-1523802000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>651656250</v>
+        <v>652312500</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-28</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-845241600</v>
+        <v>-846092800</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>23</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>337103640</v>
+        <v>337443120</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-26</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-459302220</v>
+        <v>-459764760</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1682539200</v>
+        <v>1684233600</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-23</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-890721000</v>
+        <v>-891618000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>814756500</v>
+        <v>815577000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -943,90 +943,90 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-494514000</v>
+        <v>-253072400</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>0.32%→0.28%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>51→31</t>
+          <t>108→88</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>387270000</v>
+        <v>400780800</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.50%→0.63%</t>
+          <t>0.68%→0.78%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-252817800</v>
+        <v>-495012000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.28%</t>
+          <t>0.27%→0.19%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>108→88</t>
+          <t>51→31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>400377600</v>
+        <v>1055628000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.68%→0.78%</t>
+          <t>3.96%→3.95%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1038,7 +1038,7 @@
         <v>-15</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-926469000</v>
+        <v>-927402000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1054,44 +1054,44 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1054566000</v>
+        <v>387660000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>3.96%→3.95%</t>
+          <t>0.50%→0.63%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-371183400</v>
+        <v>-432091800</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.28%</t>
+          <t>0.94%→0.99%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>368651250</v>
+        <v>369022500</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1119,90 +1119,90 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-430962000</v>
+        <v>-371557200</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.54%</t>
+          <t>0.39%→0.28%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>8</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>316568400</v>
+        <v>1522012800</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.99%→1.71%</t>
+          <t>1.98%→2.51%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>165→173</t>
+          <t>45→53</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-431657100</v>
+        <v>-431396000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.94%→0.99%</t>
+          <t>0.58%→0.54%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>8</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1520481600</v>
+        <v>316887200</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.98%→2.51%</t>
+          <t>1.99%→1.71%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>45→53</t>
+          <t>165→173</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>-11</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-767886900</v>
+        <v>-768660200</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>714463500</v>
+        <v>715183000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-217268400</v>
+        <v>-217487200</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>4</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1662282000</v>
+        <v>1663956000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-431359200</v>
+        <v>-431793600</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>603247500</v>
+        <v>603855000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-355096800</v>
+        <v>-355454400</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1367,23 +1367,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-675736500</v>
+        <v>-700770000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>9.52%→7.35%</t>
+          <t>1.24%→0.87%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-700065000</v>
+        <v>-676417000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.24%→0.87%</t>
+          <t>9.52%→7.35%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-387766500</v>
+        <v>-388157000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>-3</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-326200500</v>
+        <v>-326529000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억   ·   현금 28억(0.7%)      오늘 2026-07-27  vs  5일전 2026-07-20      매수 5종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,527억   ·   현금 26억(0.7%)      오늘 2026-07-27  vs  5일전 2026-07-20      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1570,7 +1570,7 @@
         <v>46</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1938292800</v>
+        <v>1808407200</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>-138</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-7718367600</v>
+        <v>-7201157400</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>40</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1084848000</v>
+        <v>1012152000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1083393000</v>
+        <v>1010794500</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>12</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>2098692000</v>
+        <v>1958058000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>5</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1140720000</v>
+        <v>1064280000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1717,544 +1717,519 @@
       <c r="K34" s="17" t="n"/>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="19" t="n"/>
-      <c r="F36" s="19" t="n"/>
-      <c r="G36" s="19" t="n"/>
-      <c r="H36" s="19" t="n"/>
-      <c r="I36" s="19" t="n"/>
-      <c r="J36" s="19" t="n"/>
-      <c r="K36" s="19" t="n"/>
-    </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="n"/>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="19" t="n"/>
-      <c r="E38" s="19" t="n"/>
-      <c r="F38" s="19" t="n"/>
-      <c r="G38" s="19" t="n"/>
-      <c r="H38" s="19" t="n"/>
-      <c r="I38" s="19" t="n"/>
-      <c r="J38" s="19" t="n"/>
-      <c r="K38" s="19" t="n"/>
-    </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 290억   ·   현금 1억(0.2%)      오늘 2026-07-27  vs  5일전 2026-07-20      매수 11종목  /  매도 9종목</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,302억   ·   현금 66억(2.8%)      오늘 2026-07-27  vs  5일전 2026-07-20      매수 3종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지  (신규)</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>230</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>7209948000</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→3.17%</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>0→230</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>-4709060000</v>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>9.62%→5.79%</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>190→140</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>에코프로</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>1837536800</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>1.58%→2.61%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>76→110</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>오킨스전자</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>-395367280</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>0.34%→0.18%</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>99→50</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>2316816000</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>1.66%→3.05%</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>16→24</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>-1951440000</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>7.35%→5.57%</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>150→130</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>-1014472000</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>4.23%→2.90%</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>150→130</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>-1891997200</v>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>4.02%→2.63%</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>79→60</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,238억   ·   현금 15억(0.7%)      오늘 2026-07-27  vs  5일전 2026-07-20      매수 5종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="8" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H47" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I47" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr">
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K47" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>심텍홀딩스  (신규)</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>485</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>128272800</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.44%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>0→485</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-139</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-42414460</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>2.90%→2.72%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>2,736→2,597</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>91</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>55051360</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>7.02%→7.13%</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>3,339→3,430</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>코오롱티슈진  (편출)</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-77</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>-123184600</v>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>0.43%→0.00%</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>77→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>81874800</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>5.78%→6.00%</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>772→810</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-63</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>-203490000</v>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>8.19%→7.40%</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>730→667</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>RF머트리얼즈</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="n">
-        <v>33</v>
-      </c>
-      <c r="C46" s="11" t="n">
-        <v>131670000</v>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>0.46%→0.90%</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>33→66</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>엘티씨</t>
-        </is>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>-18</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>-63475200</v>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>1.31%→1.08%</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>107→89</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="C47" s="11" t="n">
-        <v>167443200</v>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>3.04%→3.58%</t>
-        </is>
-      </c>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>141→168</t>
-        </is>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>-11</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>-57684000</v>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
-        <is>
-          <t>2.71%→2.49%</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>149→138</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>37232400</v>
+        <v>2309202000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>3.09%→3.19%</t>
+          <t>3.31%→3.95%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>550→573</t>
+          <t>296→401</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-10</v>
+        <v>-166</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-66196000</v>
+        <v>-10878710400</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>1.20%→0.96%</t>
+          <t>14.16%→9.67%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>52→42</t>
+          <t>495→329</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>140539200</v>
+        <v>2404404000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.73%→3.18%</t>
+          <t>3.07%→4.07%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>67→79</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>-44809600</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>1.19%→1.02%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>61→53</t>
-        </is>
-      </c>
+          <t>250→340</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="n"/>
+      <c r="H49" s="17" t="n"/>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="17" t="n"/>
+      <c r="K49" s="17" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>82764000</v>
+        <v>2446802100</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>2.78%→3.03%</t>
+          <t>5.04%→5.85%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>87→96</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>한중엔시에스</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-12350000</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>2.92%→2.84%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>340→335</t>
-        </is>
-      </c>
+          <t>299→368</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="n"/>
+      <c r="H50" s="17" t="n"/>
+      <c r="I50" s="17" t="n"/>
+      <c r="J50" s="17" t="n"/>
+      <c r="K50" s="17" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>59660000</v>
+        <v>2585952000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.78%→2.95%</t>
+          <t>7.73%→7.46%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>67→72</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>올릭스  (편출)</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>-25946400</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>0.09%→0.00%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>3→0</t>
-        </is>
-      </c>
+          <t>348→412</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="n"/>
+      <c r="H51" s="17" t="n"/>
+      <c r="I51" s="17" t="n"/>
+      <c r="J51" s="17" t="n"/>
+      <c r="K51" s="17" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>39550400</v>
+        <v>2328574500</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>1.07%→1.19%</t>
+          <t>9.85%→11.93%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>31→35</t>
+          <t>219→240</t>
         </is>
       </c>
       <c r="G52" s="17" t="n"/>
@@ -2263,319 +2238,836 @@
       <c r="J52" s="17" t="n"/>
       <c r="K52" s="17" t="n"/>
     </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>34443200</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>2.54%→2.63%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>85→89</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="n"/>
-      <c r="H53" s="17" t="n"/>
-      <c r="I53" s="17" t="n"/>
-      <c r="J53" s="17" t="n"/>
-      <c r="K53" s="17" t="n"/>
-    </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 484억   ·   현금 17억(3.4%)      오늘 2026-07-27  vs  5일전 2026-07-20      매수 3종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="n"/>
-      <c r="J55" s="4" t="n"/>
-      <c r="K55" s="4" t="n"/>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억   ·   현금 1억(0.2%)      오늘 2026-07-27  vs  5일전 2026-07-20      매수 11종목  /  매도 9종목</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H56" s="8" t="n"/>
-      <c r="I56" s="8" t="n"/>
-      <c r="J56" s="8" t="n"/>
-      <c r="K56" s="8" t="n"/>
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K57" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>심텍홀딩스  (신규)</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>485</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>128272800</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.44%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>0→485</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>씨에스베어링</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-139</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-42414460</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>2.90%→2.72%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>2,736→2,597</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>713286000</v>
+        <v>55051360</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>4.77%→6.98%</t>
+          <t>7.02%→7.13%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>64→82</t>
+          <t>3,339→3,430</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>큐리오시스  (편출)</t>
+          <t>코오롱티슈진  (편출)</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-593</v>
+        <v>-77</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-921522000</v>
+        <v>-123184600</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>1.84%→0.00%</t>
+          <t>0.43%→0.00%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>593→0</t>
+          <t>77→0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>197136000</v>
+        <v>81874800</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>8.37%→9.52%</t>
+          <t>5.78%→6.00%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>215→225</t>
+          <t>772→810</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>코오롱티슈진  (편출)</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-163</v>
+        <v>-63</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1123575300</v>
+        <v>-203490000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2.24%→0.00%</t>
+          <t>8.19%→7.40%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>163→0</t>
+          <t>730→667</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>131670000</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>0.46%→0.90%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>33→66</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-63475200</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>1.31%→1.08%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>107→89</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>167443200</v>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>3.04%→3.58%</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>141→168</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-57684000</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>2.71%→2.49%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>149→138</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>37232400</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>3.09%→3.19%</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>550→573</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>씨엠티엑스</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-66196000</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>1.20%→0.96%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>52→42</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>140539200</v>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>2.73%→3.18%</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>67→79</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-44809600</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>1.19%→1.02%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>61→53</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>82764000</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>2.78%→3.03%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>87→96</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-12350000</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>2.92%→2.84%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>340→335</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>59660000</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>2.78%→2.95%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>67→72</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>올릭스  (편출)</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-25946400</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>0.09%→0.00%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>3→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>34443200</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>2.54%→2.63%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>85→89</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="n"/>
+      <c r="H66" s="17" t="n"/>
+      <c r="I66" s="17" t="n"/>
+      <c r="J66" s="17" t="n"/>
+      <c r="K66" s="17" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>39550400</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>1.07%→1.19%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>31→35</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="n"/>
+      <c r="H67" s="17" t="n"/>
+      <c r="I67" s="17" t="n"/>
+      <c r="J67" s="17" t="n"/>
+      <c r="K67" s="17" t="n"/>
+    </row>
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 470억   ·   현금 16억(3.4%)      오늘 2026-07-27  vs  5일전 2026-07-20      매수 3종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="n"/>
+      <c r="I70" s="8" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>706860000</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>4.77%→6.98%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>64→82</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>큐리오시스  (편출)</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-593</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-913220000</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>1.84%→0.00%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>593→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>195360000</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>8.37%→9.52%</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>215→225</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>코오롱티슈진  (편출)</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>-163</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>-1113453000</v>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>2.24%→0.00%</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>163→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
           <t>삼성바이오로직스  (신규)</t>
         </is>
       </c>
-      <c r="B60" s="11" t="n">
+      <c r="B74" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C60" s="11" t="n">
-        <v>505494000</v>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="C74" s="11" t="n">
+        <v>500940000</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
         <is>
           <t>0.00%→1.09%</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>0→3</t>
         </is>
       </c>
-      <c r="G60" s="14" t="inlineStr">
+      <c r="G74" s="14" t="inlineStr">
         <is>
           <t>올릭스</t>
         </is>
       </c>
-      <c r="H60" s="15" t="n">
+      <c r="H74" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I60" s="15" t="n">
-        <v>-182317500</v>
-      </c>
-      <c r="J60" s="16" t="inlineStr">
+      <c r="I74" s="15" t="n">
+        <v>-180675000</v>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
         <is>
           <t>10.29%→8.48%</t>
         </is>
       </c>
-      <c r="K60" s="13" t="inlineStr">
+      <c r="K74" s="13" t="inlineStr">
         <is>
           <t>340→325</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="17" t="n"/>
-      <c r="B61" s="17" t="n"/>
-      <c r="C61" s="17" t="n"/>
-      <c r="D61" s="17" t="n"/>
-      <c r="E61" s="17" t="n"/>
-      <c r="G61" s="14" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="17" t="n"/>
+      <c r="B75" s="17" t="n"/>
+      <c r="C75" s="17" t="n"/>
+      <c r="D75" s="17" t="n"/>
+      <c r="E75" s="17" t="n"/>
+      <c r="G75" s="14" t="inlineStr">
         <is>
           <t>알테오젠</t>
         </is>
       </c>
-      <c r="H61" s="15" t="n">
+      <c r="H75" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I61" s="15" t="n">
-        <v>-266844000</v>
-      </c>
-      <c r="J61" s="16" t="inlineStr">
+      <c r="I75" s="15" t="n">
+        <v>-264440000</v>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
         <is>
           <t>8.82%→9.74%</t>
         </is>
       </c>
-      <c r="K61" s="13" t="inlineStr">
+      <c r="K75" s="13" t="inlineStr">
         <is>
           <t>144→136</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="18" t="inlineStr">
+    <row r="77" ht="19" customHeight="1">
+      <c r="A77" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B63" s="19" t="n"/>
-      <c r="C63" s="19" t="n"/>
-      <c r="D63" s="19" t="n"/>
-      <c r="E63" s="19" t="n"/>
-      <c r="F63" s="19" t="n"/>
-      <c r="G63" s="19" t="n"/>
-      <c r="H63" s="19" t="n"/>
-      <c r="I63" s="19" t="n"/>
-      <c r="J63" s="19" t="n"/>
-      <c r="K63" s="19" t="n"/>
+      <c r="B77" s="19" t="n"/>
+      <c r="C77" s="19" t="n"/>
+      <c r="D77" s="19" t="n"/>
+      <c r="E77" s="19" t="n"/>
+      <c r="F77" s="19" t="n"/>
+      <c r="G77" s="19" t="n"/>
+      <c r="H77" s="19" t="n"/>
+      <c r="I77" s="19" t="n"/>
+      <c r="J77" s="19" t="n"/>
+      <c r="K77" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="G56:K56"/>
+  <mergeCells count="21">
+    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G70:K70"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="G28:K28"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G55:K55"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A55:K55"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G28:K28"/>
-    <mergeCell ref="A63:K63"/>
-    <mergeCell ref="G41:K41"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G46:K46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260727.xlsx
+++ b/reports/pdf_rolling5_20260727.xlsx
@@ -943,23 +943,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-253072400</v>
+        <v>-495012000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.28%</t>
+          <t>0.27%→0.19%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>108→88</t>
+          <t>51→31</t>
         </is>
       </c>
     </row>
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-495012000</v>
+        <v>-253072400</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>0.32%→0.28%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>51→31</t>
+          <t>108→88</t>
         </is>
       </c>
     </row>
@@ -1119,90 +1119,90 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-371557200</v>
+        <v>-431396000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.28%</t>
+          <t>0.58%→0.54%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>8</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1522012800</v>
+        <v>316887200</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.98%→2.51%</t>
+          <t>1.99%→1.71%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>45→53</t>
+          <t>165→173</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-431396000</v>
+        <v>-371557200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.54%</t>
+          <t>0.39%→0.28%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>8</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>316887200</v>
+        <v>1522012800</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.99%→1.71%</t>
+          <t>1.98%→2.51%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>165→173</t>
+          <t>45→53</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-431793600</v>
+        <v>-355454400</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>2.29%→2.37%</t>
+          <t>1.21%→1.09%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-355454400</v>
+        <v>-431793600</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.21%→1.09%</t>
+          <t>2.29%→2.37%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
@@ -1367,23 +1367,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-700770000</v>
+        <v>-676417000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.24%→0.87%</t>
+          <t>9.52%→7.35%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-676417000</v>
+        <v>-388157000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>9.52%→7.35%</t>
+          <t>0.44%→0.39%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -1423,23 +1423,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-388157000</v>
+        <v>-700770000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.39%</t>
+          <t>1.24%→0.87%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
@@ -1917,18 +1917,18 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1951440000</v>
+        <v>-1014472000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>7.35%→5.57%</t>
+          <t>4.23%→2.90%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -1945,18 +1945,18 @@
       <c r="E42" s="17" t="n"/>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-1014472000</v>
+        <v>-1951440000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>4.23%→2.90%</t>
+          <t>7.35%→5.57%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -2337,11 +2337,11 @@
         <v>485</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>128272800</v>
+        <v>119979300</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.44%</t>
+          <t>0.00%→0.45%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2358,11 +2358,11 @@
         <v>-139</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-42414460</v>
+        <v>-40565760</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.90%→2.72%</t>
+          <t>3.02%→2.84%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2381,11 +2381,11 @@
         <v>91</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>55051360</v>
+        <v>51731680</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>7.02%→7.13%</t>
+          <t>7.17%→7.30%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2402,11 +2402,11 @@
         <v>-77</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-123184600</v>
+        <v>-87780000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>0.43%→0.00%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2425,11 +2425,11 @@
         <v>38</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>81874800</v>
+        <v>78986800</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>5.78%→6.00%</t>
+          <t>6.06%→6.30%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2446,11 +2446,11 @@
         <v>-63</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-203490000</v>
+        <v>-186732000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>8.19%→7.40%</t>
+          <t>8.17%→7.40%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2469,11 +2469,11 @@
         <v>33</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>131670000</v>
+        <v>56304600</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.46%→0.90%</t>
+          <t>0.21%→0.42%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2490,11 +2490,11 @@
         <v>-18</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-63475200</v>
+        <v>-54514800</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>1.31%→1.08%</t>
+          <t>1.22%→1.01%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2513,11 +2513,11 @@
         <v>27</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>167443200</v>
+        <v>150411600</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>3.04%→3.58%</t>
+          <t>2.97%→3.50%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2534,11 +2534,11 @@
         <v>-11</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-57684000</v>
+        <v>-51999200</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2.71%→2.49%</t>
+          <t>2.66%→2.44%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2557,11 +2557,11 @@
         <v>23</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>37232400</v>
+        <v>33212000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>3.09%→3.19%</t>
+          <t>3.00%→3.10%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2578,7 +2578,7 @@
         <v>-10</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-66196000</v>
+        <v>-61028000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2601,11 +2601,11 @@
         <v>12</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>140539200</v>
+        <v>124123200</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>2.73%→3.18%</t>
+          <t>2.62%→3.06%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -2622,11 +2622,11 @@
         <v>-8</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-44809600</v>
+        <v>-39216000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>1.19%→1.02%</t>
+          <t>1.13%→0.97%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2645,11 +2645,11 @@
         <v>9</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>82764000</v>
+        <v>72435600</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>2.78%→3.03%</t>
+          <t>2.65%→2.89%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2666,11 +2666,11 @@
         <v>-5</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-12350000</v>
+        <v>-11552000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>2.92%→2.84%</t>
+          <t>2.97%→2.90%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2689,11 +2689,11 @@
         <v>5</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>59660000</v>
+        <v>54682000</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>2.78%→2.95%</t>
+          <t>2.77%→2.95%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2710,7 +2710,7 @@
         <v>-3</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-25946400</v>
+        <v>-24966000</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2726,23 +2726,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>34443200</v>
+        <v>34412800</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2.54%→2.63%</t>
+          <t>1.01%→1.13%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>85→89</t>
+          <t>31→35</t>
         </is>
       </c>
       <c r="G66" s="17" t="n"/>
@@ -2754,23 +2754,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>39550400</v>
+        <v>30552000</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>1.07%→1.19%</t>
+          <t>2.45%→2.54%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>31→35</t>
+          <t>85→89</t>
         </is>
       </c>
       <c r="G67" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260727.xlsx
+++ b/reports/pdf_rolling5_20260727.xlsx
@@ -943,90 +943,90 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-495012000</v>
+        <v>-253072400</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>0.32%→0.28%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>51→31</t>
+          <t>108→88</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>400780800</v>
+        <v>1055628000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.68%→0.78%</t>
+          <t>3.96%→3.95%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-253072400</v>
+        <v>-495012000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.28%</t>
+          <t>0.27%→0.19%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>108→88</t>
+          <t>51→31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1055628000</v>
+        <v>387660000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3.96%→3.95%</t>
+          <t>0.50%→0.63%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>387660000</v>
+        <v>400780800</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.50%→0.63%</t>
+          <t>0.68%→0.78%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1119,90 +1119,90 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-431396000</v>
+        <v>-371557200</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.54%</t>
+          <t>0.39%→0.28%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>8</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>316887200</v>
+        <v>1522012800</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.99%→1.71%</t>
+          <t>1.98%→2.51%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>165→173</t>
+          <t>45→53</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-371557200</v>
+        <v>-431396000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.28%</t>
+          <t>0.58%→0.54%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>8</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1522012800</v>
+        <v>316887200</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.98%→2.51%</t>
+          <t>1.99%→1.71%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>45→53</t>
+          <t>165→173</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1295,23 +1295,23 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-355454400</v>
+        <v>-431793600</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.21%→1.09%</t>
+          <t>2.29%→2.37%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-431793600</v>
+        <v>-355454400</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.29%→2.37%</t>
+          <t>1.21%→1.09%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1367,23 +1367,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-676417000</v>
+        <v>-388157000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>9.52%→7.35%</t>
+          <t>0.44%→0.39%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-388157000</v>
+        <v>-676417000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.39%</t>
+          <t>9.52%→7.35%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
         <v>485</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>119979300</v>
+        <v>126429800</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2358,11 +2358,11 @@
         <v>-139</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-40565760</v>
+        <v>-38294500</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>3.02%→2.84%</t>
+          <t>2.70%→2.54%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2381,11 +2381,11 @@
         <v>91</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>51731680</v>
+        <v>51385880</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>7.17%→7.30%</t>
+          <t>6.76%→6.89%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2402,11 +2402,11 @@
         <v>-77</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-87780000</v>
+        <v>-251050800</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.00%</t>
+          <t>0.90%→0.00%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2425,11 +2425,11 @@
         <v>38</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>78986800</v>
+        <v>80719600</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>6.06%→6.30%</t>
+          <t>5.88%→6.12%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2446,11 +2446,11 @@
         <v>-63</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-186732000</v>
+        <v>-173325600</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>8.17%→7.40%</t>
+          <t>7.21%→6.53%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2469,11 +2469,11 @@
         <v>33</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>56304600</v>
+        <v>119004600</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.21%→0.42%</t>
+          <t>0.43%→0.85%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2490,11 +2490,11 @@
         <v>-18</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-54514800</v>
+        <v>-75376800</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>1.22%→1.01%</t>
+          <t>1.61%→1.33%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2513,11 +2513,11 @@
         <v>27</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>150411600</v>
+        <v>183243600</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.97%→3.50%</t>
+          <t>3.43%→4.05%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2534,11 +2534,11 @@
         <v>-11</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-51999200</v>
+        <v>-46648800</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2.66%→2.44%</t>
+          <t>2.27%→2.08%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2557,11 +2557,11 @@
         <v>23</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>33212000</v>
+        <v>36271000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>3.00%→3.10%</t>
+          <t>3.11%→3.21%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2578,11 +2578,11 @@
         <v>-10</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-61028000</v>
+        <v>-67488000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.20%→0.96%</t>
+          <t>1.26%→1.01%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2601,11 +2601,11 @@
         <v>12</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>124123200</v>
+        <v>151118400</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>2.62%→3.06%</t>
+          <t>3.03%→3.54%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -2622,11 +2622,11 @@
         <v>-8</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-39216000</v>
+        <v>-47180800</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>1.13%→0.97%</t>
+          <t>1.29%→1.11%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2645,11 +2645,11 @@
         <v>9</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>72435600</v>
+        <v>92340000</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.89%</t>
+          <t>3.20%→3.50%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2666,11 +2666,11 @@
         <v>-5</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-11552000</v>
+        <v>-10925000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>2.97%→2.90%</t>
+          <t>2.67%→2.60%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2689,11 +2689,11 @@
         <v>5</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>54682000</v>
+        <v>64600000</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>2.77%→2.95%</t>
+          <t>3.11%→3.31%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2710,7 +2710,7 @@
         <v>-3</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-24966000</v>
+        <v>-24897600</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2726,23 +2726,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>34412800</v>
+        <v>35294400</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.13%</t>
+          <t>2.69%→2.79%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>31→35</t>
+          <t>85→89</t>
         </is>
       </c>
       <c r="G66" s="17" t="n"/>
@@ -2754,23 +2754,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>30552000</v>
+        <v>43350400</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.45%→2.54%</t>
+          <t>1.21%→1.35%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>85→89</t>
+          <t>31→35</t>
         </is>
       </c>
       <c r="G67" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260727.xlsx
+++ b/reports/pdf_rolling5_20260727.xlsx
@@ -943,90 +943,90 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-253072400</v>
+        <v>-495012000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.28%</t>
+          <t>0.27%→0.19%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>108→88</t>
+          <t>51→31</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1055628000</v>
+        <v>387660000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>3.96%→3.95%</t>
+          <t>0.50%→0.63%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-495012000</v>
+        <v>-253072400</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>0.32%→0.28%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>51→31</t>
+          <t>108→88</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>387660000</v>
+        <v>1055628000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.50%→0.63%</t>
+          <t>3.96%→3.95%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-432091800</v>
+        <v>-431396000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.94%→0.99%</t>
+          <t>0.58%→0.54%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1119,23 +1119,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-371557200</v>
+        <v>-432091800</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.28%</t>
+          <t>0.94%→0.99%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-431396000</v>
+        <v>-371557200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.54%</t>
+          <t>0.39%→0.28%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -1367,23 +1367,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-388157000</v>
+        <v>-700770000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.39%</t>
+          <t>1.24%→0.87%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>30→25</t>
         </is>
       </c>
     </row>
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-676417000</v>
+        <v>-388157000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>9.52%→7.35%</t>
+          <t>0.44%→0.39%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -1423,23 +1423,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-700770000</v>
+        <v>-676417000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.24%→0.87%</t>
+          <t>9.52%→7.35%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>30→25</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -1917,18 +1917,18 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1014472000</v>
+        <v>-1951440000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>4.23%→2.90%</t>
+          <t>7.35%→5.57%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -1945,18 +1945,18 @@
       <c r="E42" s="17" t="n"/>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-1951440000</v>
+        <v>-1014472000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>7.35%→5.57%</t>
+          <t>4.23%→2.90%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -2726,23 +2726,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>35294400</v>
+        <v>43350400</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2.69%→2.79%</t>
+          <t>1.21%→1.35%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>85→89</t>
+          <t>31→35</t>
         </is>
       </c>
       <c r="G66" s="17" t="n"/>
@@ -2754,23 +2754,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>43350400</v>
+        <v>35294400</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>1.21%→1.35%</t>
+          <t>2.69%→2.79%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>31→35</t>
+          <t>85→89</t>
         </is>
       </c>
       <c r="G67" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260727.xlsx
+++ b/reports/pdf_rolling5_20260727.xlsx
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>387660000</v>
+        <v>1055628000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.50%→0.63%</t>
+          <t>3.96%→3.95%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1055628000</v>
+        <v>400780800</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3.96%→3.95%</t>
+          <t>0.68%→0.78%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1054,44 +1054,44 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>400780800</v>
+        <v>387660000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.68%→0.78%</t>
+          <t>0.50%→0.63%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-431396000</v>
+        <v>-371557200</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.54%</t>
+          <t>0.39%→0.28%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -1142,67 +1142,67 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>8</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1522012800</v>
+        <v>316887200</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.98%→2.51%</t>
+          <t>1.99%→1.71%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>45→53</t>
+          <t>165→173</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-371557200</v>
+        <v>-431396000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.28%</t>
+          <t>0.58%→0.54%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>8</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>316887200</v>
+        <v>1522012800</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.99%→1.71%</t>
+          <t>1.98%→2.51%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>165→173</t>
+          <t>45→53</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1395,23 +1395,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-388157000</v>
+        <v>-676417000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.39%</t>
+          <t>9.52%→7.35%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -1423,23 +1423,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-676417000</v>
+        <v>-388157000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>9.52%→7.35%</t>
+          <t>0.44%→0.39%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
         <v>485</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>126429800</v>
+        <v>119979300</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2358,11 +2358,11 @@
         <v>-139</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-38294500</v>
+        <v>-40565760</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.70%→2.54%</t>
+          <t>3.02%→2.84%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2381,11 +2381,11 @@
         <v>91</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>51385880</v>
+        <v>51731680</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>6.76%→6.89%</t>
+          <t>7.17%→7.30%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2402,11 +2402,11 @@
         <v>-77</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-251050800</v>
+        <v>-87780000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>0.90%→0.00%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2425,11 +2425,11 @@
         <v>38</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>80719600</v>
+        <v>78986800</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>5.88%→6.12%</t>
+          <t>6.06%→6.30%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2446,11 +2446,11 @@
         <v>-63</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-173325600</v>
+        <v>-186732000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>7.21%→6.53%</t>
+          <t>8.17%→7.40%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2469,11 +2469,11 @@
         <v>33</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>119004600</v>
+        <v>56304600</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.85%</t>
+          <t>0.21%→0.42%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2490,11 +2490,11 @@
         <v>-18</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-75376800</v>
+        <v>-54514800</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>1.61%→1.33%</t>
+          <t>1.22%→1.01%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2513,11 +2513,11 @@
         <v>27</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>183243600</v>
+        <v>150411600</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>3.43%→4.05%</t>
+          <t>2.97%→3.50%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2534,11 +2534,11 @@
         <v>-11</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-46648800</v>
+        <v>-51999200</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2.27%→2.08%</t>
+          <t>2.66%→2.44%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2557,11 +2557,11 @@
         <v>23</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>36271000</v>
+        <v>33212000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>3.11%→3.21%</t>
+          <t>3.00%→3.10%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2578,11 +2578,11 @@
         <v>-10</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-67488000</v>
+        <v>-61028000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>1.26%→1.01%</t>
+          <t>1.20%→0.96%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2601,11 +2601,11 @@
         <v>12</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>151118400</v>
+        <v>124123200</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>3.03%→3.54%</t>
+          <t>2.62%→3.06%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -2622,11 +2622,11 @@
         <v>-8</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-47180800</v>
+        <v>-39216000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>1.29%→1.11%</t>
+          <t>1.13%→0.97%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2645,11 +2645,11 @@
         <v>9</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>92340000</v>
+        <v>72435600</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>3.20%→3.50%</t>
+          <t>2.65%→2.89%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2666,11 +2666,11 @@
         <v>-5</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-10925000</v>
+        <v>-11552000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.60%</t>
+          <t>2.97%→2.90%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2689,11 +2689,11 @@
         <v>5</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>64600000</v>
+        <v>54682000</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>3.11%→3.31%</t>
+          <t>2.77%→2.95%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2710,7 +2710,7 @@
         <v>-3</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-24897600</v>
+        <v>-24966000</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2733,11 +2733,11 @@
         <v>4</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>43350400</v>
+        <v>34412800</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>1.21%→1.35%</t>
+          <t>1.01%→1.13%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2761,11 +2761,11 @@
         <v>4</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>35294400</v>
+        <v>30552000</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.69%→2.79%</t>
+          <t>2.45%→2.54%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
